--- a/Test_Data/analysis/data_v2/fig_tdd_tradeoff.xlsx
+++ b/Test_Data/analysis/data_v2/fig_tdd_tradeoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Thesis\thesis\Test_Data\analysis\data_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B121A09-8150-4182-A327-E3934A2397AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B60DF1-950A-4304-B478-12B60D26AA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1310,8 +1310,9 @@
           <c:h val="0.54918489355497224"/>
         </c:manualLayout>
       </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1328,19 +1329,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="sq" cmpd="sng">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln cap="sq" cmpd="sng">
+              <a:noFill/>
               <a:miter lim="800000"/>
               <a:headEnd type="diamond" w="sm" len="med"/>
               <a:tailEnd type="diamond" w="sm" len="med"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Slope!$I$24:$K$24</c:f>
@@ -1376,7 +1376,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-7A16-488D-80CC-F2DBE8CF29CD}"/>
@@ -1398,22 +1397,20 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:headEnd type="diamond" w="sm" len="med"/>
               <a:tailEnd type="diamond" w="sm" len="med"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Slope!$I$24:$K$24</c:f>
@@ -1449,7 +1446,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-7A16-488D-80CC-F2DBE8CF29CD}"/>
@@ -1471,19 +1467,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:headEnd type="diamond" w="sm" len="med"/>
               <a:tailEnd type="diamond" w="sm" len="med"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Slope!$I$24:$K$24</c:f>
@@ -1519,7 +1513,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-7A16-488D-80CC-F2DBE8CF29CD}"/>
@@ -1541,22 +1534,20 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
               <a:headEnd type="diamond" w="sm" len="med"/>
               <a:tailEnd type="diamond" w="sm" len="med"/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Slope!$I$24:$K$24</c:f>
@@ -1592,7 +1583,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-7A16-488D-80CC-F2DBE8CF29CD}"/>
@@ -1607,10 +1597,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
+        <c:gapWidth val="100"/>
         <c:axId val="799145312"/>
         <c:axId val="500433615"/>
-      </c:lineChart>
+      </c:barChart>
       <c:catAx>
         <c:axId val="799145312"/>
         <c:scaling>
